--- a/output2/【河洛話注音】金剛般若波羅蜜經017.xlsx
+++ b/output2/【河洛話注音】金剛般若波羅蜜經017.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7672A1BA-9B0C-4D19-BC47-957B59BC7F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD56E6AA-F054-481A-BD8A-3DBDD9471F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="5475" yWindow="3945" windowWidth="31875" windowHeight="11295" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="502">
   <si>
     <t>【台羅拼音】</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1980,10 +1980,6 @@
   </si>
   <si>
     <t>ㄉㄧㆻ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hiu2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6466,16 +6462,16 @@
         <v>327</v>
       </c>
       <c r="E64" s="85" t="s">
-        <v>437</v>
+        <v>300</v>
       </c>
       <c r="F64" s="85"/>
       <c r="G64" s="85"/>
       <c r="H64" s="85"/>
       <c r="I64" s="85" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J64" s="85" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K64" s="85"/>
       <c r="L64" s="85" t="s">
@@ -6492,7 +6488,7 @@
         <v>309</v>
       </c>
       <c r="Q64" s="85" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R64" s="85" t="s">
         <v>331</v>
@@ -6559,16 +6555,16 @@
         <v>328</v>
       </c>
       <c r="E66" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F66" s="86"/>
       <c r="G66" s="86"/>
       <c r="H66" s="86"/>
       <c r="I66" s="86" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J66" s="86" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K66" s="86"/>
       <c r="L66" s="86" t="s">
@@ -6585,7 +6581,7 @@
         <v>310</v>
       </c>
       <c r="Q66" s="86" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="R66" s="86" t="s">
         <v>332</v>
@@ -6619,10 +6615,10 @@
         <v>423</v>
       </c>
       <c r="E68" s="85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F68" s="85" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G68" s="85"/>
       <c r="H68" s="85" t="s">
@@ -6718,10 +6714,10 @@
         <v>424</v>
       </c>
       <c r="E70" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F70" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G70" s="86"/>
       <c r="H70" s="86" t="s">
@@ -7447,10 +7443,10 @@
         <v>419</v>
       </c>
       <c r="P88" s="85" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q88" s="85" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R88" s="85" t="s">
         <v>309</v>
@@ -7548,10 +7544,10 @@
         <v>420</v>
       </c>
       <c r="P90" s="86" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q90" s="86" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R90" s="86" t="s">
         <v>310</v>
@@ -7585,12 +7581,12 @@
         <v>417</v>
       </c>
       <c r="E92" s="85" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F92" s="85"/>
       <c r="G92" s="85"/>
       <c r="H92" s="85" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I92" s="85" t="s">
         <v>425</v>
@@ -7608,17 +7604,17 @@
         <v>435</v>
       </c>
       <c r="N92" s="85" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O92" s="85" t="s">
         <v>331</v>
       </c>
       <c r="P92" s="85"/>
       <c r="Q92" s="85" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="R92" s="85" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S92" s="94"/>
       <c r="V92" s="60"/>
@@ -7682,12 +7678,12 @@
         <v>418</v>
       </c>
       <c r="E94" s="86" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F94" s="86"/>
       <c r="G94" s="86"/>
       <c r="H94" s="86" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I94" s="86" t="s">
         <v>426</v>
@@ -7705,17 +7701,17 @@
         <v>436</v>
       </c>
       <c r="N94" s="86" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O94" s="86" t="s">
         <v>332</v>
       </c>
       <c r="P94" s="86"/>
       <c r="Q94" s="86" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R94" s="86" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="S94" s="97"/>
       <c r="V94" s="60"/>
@@ -7743,13 +7739,13 @@
     <row r="96" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="56"/>
       <c r="D96" s="85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E96" s="85" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F96" s="85" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G96" s="85"/>
       <c r="H96" s="85"/>
@@ -7840,13 +7836,13 @@
     <row r="98" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="58"/>
       <c r="D98" s="86" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E98" s="86" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F98" s="86" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G98" s="86"/>
       <c r="H98" s="86"/>
@@ -7938,7 +7934,7 @@
         <v>331</v>
       </c>
       <c r="P100" s="85" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q100" s="85" t="s">
         <v>309</v>
@@ -8039,7 +8035,7 @@
         <v>332</v>
       </c>
       <c r="P102" s="86" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q102" s="86" t="s">
         <v>310</v>
@@ -8073,11 +8069,11 @@
     <row r="104" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B104" s="56"/>
       <c r="D104" s="85" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E104" s="85"/>
       <c r="F104" s="85" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G104" s="85" t="s">
         <v>389</v>
@@ -8088,7 +8084,7 @@
       <c r="I104" s="85"/>
       <c r="J104" s="85"/>
       <c r="K104" s="85" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L104" s="85" t="s">
         <v>425</v>
@@ -8107,7 +8103,7 @@
         <v>435</v>
       </c>
       <c r="R104" s="85" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="S104" s="94"/>
       <c r="V104" s="60"/>
@@ -8168,11 +8164,11 @@
     <row r="106" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="58"/>
       <c r="D106" s="86" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E106" s="86"/>
       <c r="F106" s="86" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G106" s="86" t="s">
         <v>390</v>
@@ -8183,7 +8179,7 @@
       <c r="I106" s="86"/>
       <c r="J106" s="86"/>
       <c r="K106" s="86" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L106" s="86" t="s">
         <v>426</v>
@@ -8202,7 +8198,7 @@
         <v>436</v>
       </c>
       <c r="R106" s="86" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="S106" s="97"/>
       <c r="V106" s="60"/>
@@ -8234,19 +8230,19 @@
       </c>
       <c r="E108" s="85"/>
       <c r="F108" s="85" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G108" s="85" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H108" s="85" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I108" s="85" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J108" s="85" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K108" s="85"/>
       <c r="L108" s="85"/>
@@ -8307,19 +8303,19 @@
       </c>
       <c r="E110" s="86"/>
       <c r="F110" s="86" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G110" s="86" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H110" s="86" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I110" s="86" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J110" s="86" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K110" s="86"/>
       <c r="L110" s="86"/>
@@ -8380,7 +8376,7 @@
         <v>419</v>
       </c>
       <c r="O112" s="85" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P112" s="85" t="s">
         <v>349</v>
@@ -8389,7 +8385,7 @@
         <v>387</v>
       </c>
       <c r="R112" s="85" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="S112" s="94"/>
       <c r="V112" s="60"/>
@@ -8475,7 +8471,7 @@
         <v>420</v>
       </c>
       <c r="O114" s="86" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P114" s="86" t="s">
         <v>350</v>
@@ -8484,7 +8480,7 @@
         <v>388</v>
       </c>
       <c r="R114" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="S114" s="97"/>
       <c r="V114" s="60"/>
@@ -9172,7 +9168,7 @@
     <row r="132" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B132" s="56"/>
       <c r="D132" s="85" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E132" s="85" t="s">
         <v>307</v>
@@ -9184,7 +9180,7 @@
         <v>307</v>
       </c>
       <c r="H132" s="85" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I132" s="85"/>
       <c r="J132" s="85" t="s">
@@ -9200,7 +9196,7 @@
         <v>429</v>
       </c>
       <c r="N132" s="85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O132" s="85" t="s">
         <v>395</v>
@@ -9271,7 +9267,7 @@
     <row r="134" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B134" s="58"/>
       <c r="D134" s="86" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E134" s="86" t="s">
         <v>308</v>
@@ -9283,7 +9279,7 @@
         <v>308</v>
       </c>
       <c r="H134" s="86" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I134" s="86"/>
       <c r="J134" s="86" t="s">
@@ -9299,7 +9295,7 @@
         <v>430</v>
       </c>
       <c r="N134" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="O134" s="86" t="s">
         <v>396</v>
@@ -9337,7 +9333,7 @@
     <row r="136" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B136" s="56"/>
       <c r="D136" s="85" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E136" s="85" t="s">
         <v>389</v>
@@ -9398,7 +9394,7 @@
     <row r="138" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B138" s="58"/>
       <c r="D138" s="86" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E138" s="86" t="s">
         <v>390</v>
@@ -9619,7 +9615,7 @@
         <v>409</v>
       </c>
       <c r="J144" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K144" s="85" t="s">
         <v>395</v>
@@ -9702,7 +9698,7 @@
         <v>410</v>
       </c>
       <c r="J146" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K146" s="86" t="s">
         <v>396</v>
@@ -9756,7 +9752,7 @@
       </c>
       <c r="I148" s="85"/>
       <c r="J148" s="85" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K148" s="85" t="s">
         <v>387</v>
@@ -9765,13 +9761,13 @@
         <v>347</v>
       </c>
       <c r="M148" s="85" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N148" s="85" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O148" s="85" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P148" s="85"/>
       <c r="Q148" s="85"/>
@@ -9849,7 +9845,7 @@
       </c>
       <c r="I150" s="86"/>
       <c r="J150" s="86" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K150" s="86" t="s">
         <v>388</v>
@@ -9858,13 +9854,13 @@
         <v>348</v>
       </c>
       <c r="M150" s="86" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N150" s="86" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="O150" s="86" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P150" s="86"/>
       <c r="Q150" s="86"/>
@@ -9921,19 +9917,19 @@
         <v>429</v>
       </c>
       <c r="N152" s="85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O152" s="85" t="s">
         <v>347</v>
       </c>
       <c r="P152" s="85" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q152" s="85" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R152" s="85" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S152" s="94"/>
       <c r="V152" s="60"/>
@@ -10018,19 +10014,19 @@
         <v>430</v>
       </c>
       <c r="N154" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="O154" s="86" t="s">
         <v>348</v>
       </c>
       <c r="P154" s="86" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q154" s="86" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="R154" s="86" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S154" s="97"/>
       <c r="V154" s="60"/>
@@ -10062,29 +10058,29 @@
         <v>419</v>
       </c>
       <c r="F156" s="85" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G156" s="85" t="s">
         <v>421</v>
       </c>
       <c r="H156" s="85" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I156" s="85" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J156" s="85"/>
       <c r="K156" s="85" t="s">
         <v>389</v>
       </c>
       <c r="L156" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M156" s="85" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N156" s="85" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="O156" s="85"/>
       <c r="P156" s="85"/>
@@ -10149,29 +10145,29 @@
         <v>420</v>
       </c>
       <c r="F158" s="86" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G158" s="86" t="s">
         <v>422</v>
       </c>
       <c r="H158" s="86" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I158" s="86" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J158" s="86"/>
       <c r="K158" s="86" t="s">
         <v>390</v>
       </c>
       <c r="L158" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M158" s="86" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N158" s="86" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O158" s="86"/>
       <c r="P158" s="86"/>
@@ -10222,7 +10218,7 @@
         <v>413</v>
       </c>
       <c r="M160" s="85" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N160" s="85" t="s">
         <v>387</v>
@@ -10235,7 +10231,7 @@
         <v>411</v>
       </c>
       <c r="R160" s="85" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="S160" s="94"/>
       <c r="V160" s="60"/>
@@ -10315,7 +10311,7 @@
         <v>414</v>
       </c>
       <c r="M162" s="86" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N162" s="86" t="s">
         <v>388</v>
@@ -10328,7 +10324,7 @@
         <v>412</v>
       </c>
       <c r="R162" s="86" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="S162" s="97"/>
       <c r="V162" s="60"/>
@@ -10379,7 +10375,7 @@
         <v>307</v>
       </c>
       <c r="M164" s="85" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N164" s="85" t="s">
         <v>399</v>
@@ -10474,7 +10470,7 @@
         <v>308</v>
       </c>
       <c r="M166" s="86" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N166" s="86" t="s">
         <v>400</v>
@@ -10513,10 +10509,10 @@
       <c r="B168" s="56"/>
       <c r="C168" s="1"/>
       <c r="D168" s="85" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E168" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F168" s="85" t="s">
         <v>325</v>
@@ -10608,10 +10604,10 @@
       <c r="B170" s="58"/>
       <c r="C170" s="1"/>
       <c r="D170" s="86" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E170" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F170" s="86" t="s">
         <v>326</v>
@@ -10677,10 +10673,10 @@
       </c>
       <c r="F172" s="85"/>
       <c r="G172" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H172" s="85" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I172" s="85" t="s">
         <v>325</v>
@@ -10699,7 +10695,7 @@
         <v>331</v>
       </c>
       <c r="O172" s="85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P172" s="85"/>
       <c r="Q172" s="85"/>
@@ -10770,10 +10766,10 @@
       </c>
       <c r="F174" s="86"/>
       <c r="G174" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H174" s="86" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I174" s="86" t="s">
         <v>326</v>
@@ -10792,7 +10788,7 @@
         <v>332</v>
       </c>
       <c r="O174" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P174" s="86"/>
       <c r="Q174" s="86"/>
@@ -11001,7 +10997,7 @@
         <v>413</v>
       </c>
       <c r="O180" s="85" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="P180" s="85" t="s">
         <v>389</v>
@@ -11092,7 +11088,7 @@
         <v>414</v>
       </c>
       <c r="O182" s="86" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P182" s="86" t="s">
         <v>390</v>
@@ -11132,16 +11128,16 @@
         <v>383</v>
       </c>
       <c r="G184" s="85" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H184" s="85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I184" s="85" t="s">
         <v>331</v>
       </c>
       <c r="J184" s="85" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K184" s="85"/>
       <c r="L184" s="85"/>
@@ -11149,10 +11145,10 @@
         <v>389</v>
       </c>
       <c r="N184" s="85" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="O184" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P184" s="85" t="s">
         <v>325</v>
@@ -11225,16 +11221,16 @@
         <v>384</v>
       </c>
       <c r="G186" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H186" s="86" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I186" s="86" t="s">
         <v>332</v>
       </c>
       <c r="J186" s="86" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K186" s="86"/>
       <c r="L186" s="86"/>
@@ -11242,10 +11238,10 @@
         <v>390</v>
       </c>
       <c r="N186" s="86" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O186" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P186" s="86" t="s">
         <v>326</v>
@@ -11294,19 +11290,19 @@
         <v>429</v>
       </c>
       <c r="J188" s="85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K188" s="85" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L188" s="85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M188" s="85" t="s">
         <v>331</v>
       </c>
       <c r="N188" s="85" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O188" s="85" t="s">
         <v>381</v>
@@ -11391,19 +11387,19 @@
         <v>430</v>
       </c>
       <c r="J190" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K190" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L190" s="86" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="M190" s="86" t="s">
         <v>332</v>
       </c>
       <c r="N190" s="86" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O190" s="86" t="s">
         <v>382</v>
@@ -11439,23 +11435,23 @@
       <c r="B192" s="56"/>
       <c r="C192" s="1"/>
       <c r="D192" s="85" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E192" s="85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F192" s="85"/>
       <c r="G192" s="85" t="s">
         <v>389</v>
       </c>
       <c r="H192" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I192" s="85" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J192" s="85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K192" s="85"/>
       <c r="L192" s="85" t="s">
@@ -11534,23 +11530,23 @@
       <c r="B194" s="58"/>
       <c r="C194" s="1"/>
       <c r="D194" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E194" s="86" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F194" s="86"/>
       <c r="G194" s="86" t="s">
         <v>390</v>
       </c>
       <c r="H194" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I194" s="86" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J194" s="86" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K194" s="86"/>
       <c r="L194" s="86" t="s">
@@ -11596,10 +11592,10 @@
       <c r="B196" s="56"/>
       <c r="C196" s="1"/>
       <c r="D196" s="85" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E196" s="85" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F196" s="85" t="s">
         <v>307</v>
@@ -11621,13 +11617,13 @@
         <v>429</v>
       </c>
       <c r="M196" s="85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N196" s="85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="O196" s="85" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P196" s="85" t="s">
         <v>389</v>
@@ -11695,10 +11691,10 @@
       <c r="B198" s="58"/>
       <c r="C198" s="1"/>
       <c r="D198" s="86" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E198" s="86" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F198" s="86" t="s">
         <v>308</v>
@@ -11720,13 +11716,13 @@
         <v>430</v>
       </c>
       <c r="M198" s="86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N198" s="86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="O198" s="86" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P198" s="86" t="s">
         <v>390</v>
